--- a/demo/close-tieout/spreadsheet/close-tieout-le-map/1_close-tieout-le-map_golden.xlsx
+++ b/demo/close-tieout/spreadsheet/close-tieout-le-map/1_close-tieout-le-map_golden.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LE Mapping" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corvus LE Reference" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1063,4 +1064,882 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B86"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Corvus LE</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Corvus LE ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Corvus LE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Corvus LE ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chalbury Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>7144</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>XD3 SPV L.P.</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3456</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Skarsmont Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>8499</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>X3 Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>DR3 Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5825</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DR3-AIV Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9898</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Vossthorpe Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5207</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>H JX3 Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kestrel Stroudholm (A) Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Kestrel Stroudholm Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Kestrel Gelmont Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>6009</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kestrel Westvale Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5412</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Kestrel Ravshaw Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5792</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Kestrel V3 Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Kestrel Lammwick Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kestrel Co-Invest N II, L.P.</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5043</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Kestrel DEK 1 Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Kestrel Carrshaw Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4143</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Kestrel Zellthorpe Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4883</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Kestrel Skarsshaw 10 Co-Invest 1 LP</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Kestrel Skarsshaw 9 Co-Invest 1 LP</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Kestrel Merrbury Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4003</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Kestrel Zellshaw Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4345</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Kestrel Ravthorpe A Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4447</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Kestrel Ravthorpe B Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Kestrel Ravthorpe C Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Kestrel Y3 Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Kestrel Selbeck Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4774</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Kestrel J3 Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Kestrel Kelmwold 2 2018 Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Kestrel Kelmwold 2 Caldfield Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2822</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Kestrel Kelmwold 3 Co-Invest 1 LP</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>8133</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Kestrel Kelmwold 4 Co-Invest 1 LP</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Kestrel V4 Co-Invest Lp</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>5120</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Kestrel XY3 Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>5109</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Kestrel J4 Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2844</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Kestrel Y4 Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>5934</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Kestrel J5 B Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>6032</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Kestrel J5 Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>5269</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Kestrel D4 Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>5104</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Kestrel Dunwick Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>5589</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Kestrel Brinley Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>5323</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Kestrel Mardale Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4740</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Kestrel Ravdale 1 Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>7008</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Kestrel Ravdale 2 Co-Invest 1 LP</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Kestrel Ravdale 3 Co-Invest 1 LP</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>7736</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Kestrel Renholm Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Kestrel JD3 Co-Invest</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>8231</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Kestrel Lanwold Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4837</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Kestrel DJ3 Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>6909</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Kestrel Gelworth Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>6844</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Kestrel Norbeck Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Kestrel Roskberg Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Kestrel Dunley Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>9451</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Kestrel Dunley II Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Kestrelcap Co-Invest 2 LP</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4370</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Kestrelcap Co-Invest 3 LP</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>7189</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Kestrelcap Co-Invest 4 LP</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>4060</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Kestrelcap Haslholm Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>9201</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Kestrelcap Haldbury Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>5733</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Kestrelcap Ostcombe Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>5052</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Kestrelcap Principal Opportunities LP</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>8345</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Kestrelcap XED Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ZIM LP</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>4450</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>JEG 25 AIV Co-Invest, L.P.</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>5421</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>JEG 25 Co-Invest, L.P.</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>YD4 Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>7805</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Larchdale Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>6432</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PEH 1 Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2698</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>J5 C Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>8020</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>J5 D Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>8245</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>D6 Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>9342</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Y7 Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>4481</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>D8 Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>7327</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>YX3 Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>4682</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DJ4 Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Ravdale 4 Co-Invest LP</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Ashcombe Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>D7 Co-Invest L.P</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>3301</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Renwold 2 Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Renwold Co Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>4159</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Jerrworth Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>5442</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Tarnfield (No 2) Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Tarnfield Co-Invest L.P.</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>9807</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>